--- a/jira_export_2026-08-25.xlsx
+++ b/jira_export_2026-08-25.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>16,407 €</t>
+          <t>21,099 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -760,14 +760,14 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>6,589 €</t>
+          <t>8,950 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>9,818 €</t>
+          <t>12,149 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>385 h</t>
+          <t>387 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -886,7 +886,7 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>267</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P142"/>
+  <dimension ref="A1:P144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="14" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="L6" s="14" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -1253,10 +1253,10 @@
         <v>0</v>
       </c>
       <c r="O7" s="12" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="P7" s="12" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
     </row>
     <row r="8">
@@ -1455,16 +1455,8 @@
       <c r="K10" s="14" t="n">
         <v>0.25</v>
       </c>
-      <c r="L10" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34970</t>
-        </is>
-      </c>
-      <c r="M10" s="14" t="inlineStr">
-        <is>
-          <t>00146508</t>
-        </is>
-      </c>
+      <c r="L10" s="14" t="inlineStr"/>
+      <c r="M10" s="14" t="inlineStr"/>
       <c r="N10" s="15" t="n">
         <v>0</v>
       </c>
@@ -1818,7 +1810,7 @@
         </is>
       </c>
       <c r="N15" s="12" t="n">
-        <v>429.3</v>
+        <v>0</v>
       </c>
       <c r="O15" s="12" t="n">
         <v>429.3</v>
@@ -1890,10 +1882,10 @@
         </is>
       </c>
       <c r="N16" s="15" t="n">
-        <v>789.5</v>
-      </c>
-      <c r="O16" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O16" s="15" t="n">
+        <v>394.75</v>
       </c>
       <c r="P16" s="15" t="n">
         <v>0</v>
@@ -1962,10 +1954,10 @@
         </is>
       </c>
       <c r="N17" s="12" t="n">
-        <v>430</v>
-      </c>
-      <c r="O17" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O17" s="12" t="n">
+        <v>215</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>0</v>
@@ -2034,10 +2026,10 @@
         </is>
       </c>
       <c r="N18" s="15" t="n">
-        <v>400</v>
-      </c>
-      <c r="O18" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O18" s="15" t="n">
+        <v>200</v>
       </c>
       <c r="P18" s="15" t="n">
         <v>0</v>
@@ -2685,10 +2677,10 @@
         <v>4536</v>
       </c>
       <c r="O27" s="16" t="n">
-        <v>1080</v>
+        <v>1296</v>
       </c>
       <c r="P27" s="12" t="n">
-        <v>70.81999999999999</v>
+        <v>84.98</v>
       </c>
     </row>
     <row r="28">
@@ -3677,10 +3669,10 @@
         <v>0</v>
       </c>
       <c r="O41" s="12" t="n">
-        <v>416.29</v>
+        <v>438.2</v>
       </c>
       <c r="P41" s="12" t="n">
-        <v>46.25</v>
+        <v>48.69</v>
       </c>
     </row>
     <row r="42">
@@ -3821,10 +3813,10 @@
         <v>0</v>
       </c>
       <c r="O43" s="12" t="n">
-        <v>0</v>
+        <v>66.55</v>
       </c>
       <c r="P43" s="12" t="n">
-        <v>0</v>
+        <v>133.1</v>
       </c>
     </row>
     <row r="44">
@@ -3892,11 +3884,11 @@
       <c r="N44" s="15" t="n">
         <v>920</v>
       </c>
-      <c r="O44" s="16" t="n">
-        <v>0</v>
+      <c r="O44" s="15" t="n">
+        <v>966</v>
       </c>
       <c r="P44" s="15" t="n">
-        <v>0</v>
+        <v>483</v>
       </c>
     </row>
     <row r="45">
@@ -3965,10 +3957,10 @@
         <v>4424</v>
       </c>
       <c r="O45" s="16" t="n">
-        <v>0</v>
+        <v>821.6</v>
       </c>
       <c r="P45" s="12" t="n">
-        <v>0</v>
+        <v>821.6</v>
       </c>
     </row>
     <row r="46">
@@ -4406,32 +4398,32 @@
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33311</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t>[AMIENS METROPOLE] -  Développement tableau facture terrasses</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>AMIENS METROPOLE</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve"> MM - Up - LiExp - Dev tableau facture terrasses</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -4446,7 +4438,7 @@
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J52" s="14" t="n">
@@ -4457,19 +4449,19 @@
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33272</t>
+          <t>PDMDEP-33315</t>
         </is>
       </c>
       <c r="M52" s="14" t="inlineStr">
         <is>
-          <t>00166910</t>
+          <t>00167138</t>
         </is>
       </c>
       <c r="N52" s="15" t="n">
-        <v>500</v>
-      </c>
-      <c r="O52" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O52" s="15" t="n">
+        <v>224.76</v>
       </c>
       <c r="P52" s="15" t="n">
         <v>0</v>
@@ -4478,27 +4470,27 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
@@ -4513,12 +4505,12 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J53" s="11" t="n">
@@ -4529,16 +4521,16 @@
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>149</v>
+        <v>500</v>
       </c>
       <c r="O53" s="16" t="n">
         <v>0</v>
@@ -4550,32 +4542,32 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
@@ -4585,38 +4577,38 @@
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J54" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K54" s="14" t="n">
-        <v>7.38</v>
+        <v>0</v>
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N54" s="15" t="n">
-        <v>625</v>
+        <v>149</v>
       </c>
       <c r="O54" s="16" t="n">
-        <v>607.5</v>
+        <v>0</v>
       </c>
       <c r="P54" s="15" t="n">
-        <v>82.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -4673,53 +4665,53 @@
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>0</v>
+        <v>625</v>
       </c>
       <c r="O55" s="12" t="n">
-        <v>0</v>
+        <v>652.5</v>
       </c>
       <c r="P55" s="12" t="n">
-        <v>0</v>
+        <v>88.47</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33170</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>Commune de Bonneville</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
@@ -4729,49 +4721,49 @@
       </c>
       <c r="H56" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J56" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K56" s="14" t="n">
-        <v>5</v>
+        <v>7.38</v>
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33177</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M56" s="14" t="inlineStr">
         <is>
-          <t>00166356</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N56" s="15" t="n">
-        <v>910</v>
+        <v>0</v>
       </c>
       <c r="O56" s="15" t="n">
-        <v>910</v>
+        <v>192</v>
       </c>
       <c r="P56" s="15" t="n">
-        <v>182</v>
+        <v>26.03</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33064</t>
+          <t>PDMDEP-33170</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
@@ -4781,12 +4773,12 @@
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LONGWY</t>
+          <t>Commune de Bonneville</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
@@ -4806,59 +4798,59 @@
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J57" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33073</t>
+          <t>PDMDEP-33177</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>00165708</t>
+          <t>00166356</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>1207</v>
-      </c>
-      <c r="O57" s="16" t="n">
-        <v>0</v>
+        <v>910</v>
+      </c>
+      <c r="O57" s="12" t="n">
+        <v>910</v>
       </c>
       <c r="P57" s="12" t="n">
-        <v>0</v>
+        <v>182</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33012</t>
+          <t>PDMDEP-33064</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE GRASSE</t>
+          <t>MAIRIE DE LONGWY</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
@@ -4878,64 +4870,64 @@
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="J58" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K58" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33021</t>
+          <t>PDMDEP-33073</t>
         </is>
       </c>
       <c r="M58" s="14" t="inlineStr">
         <is>
-          <t>00165368</t>
+          <t>00165708</t>
         </is>
       </c>
       <c r="N58" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="15" t="n">
-        <v>323.7</v>
+        <v>1207</v>
+      </c>
+      <c r="O58" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P58" s="15" t="n">
-        <v>1294.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33012</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE GRASSE</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr">
@@ -4945,69 +4937,69 @@
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33021</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165368</t>
         </is>
       </c>
       <c r="N59" s="12" t="n">
-        <v>500</v>
-      </c>
-      <c r="O59" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O59" s="12" t="n">
+        <v>323.7</v>
       </c>
       <c r="P59" s="12" t="n">
-        <v>0</v>
+        <v>1294.8</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32967</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 2/2</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
@@ -5017,7 +5009,7 @@
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I60" s="14" t="inlineStr">
@@ -5029,20 +5021,20 @@
         <v>4</v>
       </c>
       <c r="K60" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32974</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M60" s="14" t="inlineStr">
         <is>
-          <t>00165260</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N60" s="15" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="O60" s="16" t="n">
         <v>0</v>
@@ -5054,32 +5046,32 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-32967</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr">
@@ -5089,34 +5081,34 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J61" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-32974</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00165260</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" s="12" t="n">
+        <v>400</v>
+      </c>
+      <c r="O61" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P61" s="12" t="n">
@@ -5126,32 +5118,32 @@
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32950</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 1/2 (Pax + Mise en service)</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Migration GeODP Placier 1/2</t>
         </is>
       </c>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
@@ -5161,49 +5153,49 @@
       </c>
       <c r="H62" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J62" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K62" s="14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="L62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32958</t>
         </is>
       </c>
       <c r="M62" s="14" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00165249</t>
         </is>
       </c>
       <c r="N62" s="15" t="n">
-        <v>1294.224</v>
-      </c>
-      <c r="O62" s="16" t="n">
-        <v>219.36</v>
+        <v>0</v>
+      </c>
+      <c r="O62" s="15" t="n">
+        <v>250</v>
       </c>
       <c r="P62" s="15" t="n">
-        <v>79.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32565</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>[CD 22] - Afficher les AP signé avant MEP WFS</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
@@ -5213,12 +5205,12 @@
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CONSEIL DEPARTEMENTAL DES COTES D'ARMOR] </t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>Afficher les AP signé avant MEP WFS</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
@@ -5228,7 +5220,7 @@
       </c>
       <c r="G63" s="11" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H63" s="11" t="inlineStr">
@@ -5238,17 +5230,25 @@
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="L63" s="11" t="inlineStr"/>
-      <c r="M63" s="11" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L63" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-32772</t>
+        </is>
+      </c>
+      <c r="M63" s="11" t="inlineStr">
+        <is>
+          <t>00163806</t>
+        </is>
+      </c>
       <c r="N63" s="12" t="n">
         <v>0</v>
       </c>
@@ -5262,12 +5262,12 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
@@ -5277,12 +5277,12 @@
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F64" s="14" t="inlineStr">
@@ -5302,101 +5302,93 @@
       </c>
       <c r="I64" s="14" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J64" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K64" s="14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="L64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M64" s="14" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N64" s="15" t="n">
-        <v>142.1</v>
+        <v>1294.224</v>
       </c>
       <c r="O64" s="16" t="n">
-        <v>0</v>
+        <v>219.36</v>
       </c>
       <c r="P64" s="15" t="n">
-        <v>0</v>
+        <v>79.77</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32565</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CD 22] - Afficher les AP signé avant MEP WFS</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t xml:space="preserve">[CONSEIL DEPARTEMENTAL DES COTES D'ARMOR] </t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Afficher les AP signé avant MEP WFS</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-32470</t>
-        </is>
-      </c>
-      <c r="M65" s="11" t="inlineStr">
-        <is>
-          <t>00161950</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="L65" s="11" t="inlineStr"/>
+      <c r="M65" s="11" t="inlineStr"/>
       <c r="N65" s="12" t="n">
-        <v>2335</v>
-      </c>
-      <c r="O65" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P65" s="12" t="n">
@@ -5406,27 +5398,27 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32442</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F66" s="14" t="inlineStr">
@@ -5446,29 +5438,29 @@
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J66" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K66" s="14" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32446</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M66" s="14" t="inlineStr">
         <is>
-          <t>00161842</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N66" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" s="15" t="n">
+        <v>142.1</v>
+      </c>
+      <c r="O66" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P66" s="15" t="n">
@@ -5478,27 +5470,27 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
@@ -5518,7 +5510,7 @@
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
@@ -5529,16 +5521,16 @@
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>450</v>
+        <v>2335</v>
       </c>
       <c r="O67" s="16" t="n">
         <v>0</v>
@@ -5550,12 +5542,12 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32442</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
@@ -5565,12 +5557,12 @@
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="F68" s="14" t="inlineStr">
@@ -5590,29 +5582,29 @@
       </c>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="J68" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K68" s="14" t="n">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="L68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32446</t>
         </is>
       </c>
       <c r="M68" s="14" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161842</t>
         </is>
       </c>
       <c r="N68" s="15" t="n">
-        <v>910</v>
-      </c>
-      <c r="O68" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P68" s="15" t="n">
@@ -5622,23 +5614,27 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32152</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
-        </is>
-      </c>
-      <c r="C69" s="11" t="inlineStr"/>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="inlineStr">
+        <is>
+          <t>Maxime PONTONNIER</t>
+        </is>
+      </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAVAILLON</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
@@ -5658,7 +5654,7 @@
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
@@ -5669,16 +5665,16 @@
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32161</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>00160661</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>255</v>
+        <v>450</v>
       </c>
       <c r="O69" s="16" t="n">
         <v>0</v>
@@ -5690,32 +5686,32 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G70" s="14" t="inlineStr">
@@ -5725,64 +5721,60 @@
       </c>
       <c r="H70" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I70" s="14" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J70" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K70" s="14" t="n">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N70" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" s="15" t="n">
-        <v>100</v>
+        <v>910</v>
+      </c>
+      <c r="O70" s="16" t="n">
+        <v>91</v>
       </c>
       <c r="P70" s="15" t="n">
-        <v>400</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32152</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
-        </is>
-      </c>
-      <c r="C71" s="11" t="inlineStr">
-        <is>
-          <t>Maxime PONTONNIER</t>
-        </is>
-      </c>
+          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="inlineStr"/>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>COMMUNE DE CAVAILLON</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
@@ -5797,12 +5789,12 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J71" s="11" t="n">
@@ -5813,16 +5805,16 @@
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32161</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00160661</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
-        <v>590.15</v>
+        <v>255</v>
       </c>
       <c r="O71" s="16" t="n">
         <v>0</v>
@@ -5834,27 +5826,27 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F72" s="14" t="inlineStr">
@@ -5874,64 +5866,64 @@
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J72" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K72" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M72" s="14" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N72" s="15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O72" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O72" s="15" t="n">
+        <v>100</v>
       </c>
       <c r="P72" s="15" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr">
@@ -5946,29 +5938,29 @@
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>11.75</v>
+        <v>0</v>
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O73" s="12" t="n">
+        <v>590.15</v>
+      </c>
+      <c r="O73" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P73" s="12" t="n">
@@ -5978,12 +5970,12 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
@@ -5993,12 +5985,12 @@
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F74" s="14" t="inlineStr">
@@ -6013,12 +6005,12 @@
       </c>
       <c r="H74" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J74" s="14" t="n">
@@ -6029,16 +6021,16 @@
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N74" s="15" t="n">
-        <v>285</v>
+        <v>1000</v>
       </c>
       <c r="O74" s="16" t="n">
         <v>0</v>
@@ -6050,12 +6042,12 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
@@ -6065,12 +6057,12 @@
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
@@ -6085,34 +6077,34 @@
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0</v>
+        <v>11.75</v>
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
-        <v>1325</v>
-      </c>
-      <c r="O75" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P75" s="12" t="n">
@@ -6122,32 +6114,32 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G76" s="14" t="inlineStr">
@@ -6162,7 +6154,7 @@
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J76" s="14" t="n">
@@ -6173,16 +6165,16 @@
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N76" s="15" t="n">
-        <v>120</v>
+        <v>285</v>
       </c>
       <c r="O76" s="16" t="n">
         <v>0</v>
@@ -6194,32 +6186,32 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G77" s="11" t="inlineStr">
@@ -6229,12 +6221,12 @@
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J77" s="11" t="n">
@@ -6245,16 +6237,16 @@
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
-        <v>588</v>
+        <v>1325</v>
       </c>
       <c r="O77" s="16" t="n">
         <v>0</v>
@@ -6266,32 +6258,32 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G78" s="14" t="inlineStr">
@@ -6301,32 +6293,32 @@
       </c>
       <c r="H78" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J78" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K78" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M78" s="14" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N78" s="15" t="n">
-        <v>203.5</v>
+        <v>120</v>
       </c>
       <c r="O78" s="16" t="n">
         <v>0</v>
@@ -6338,27 +6330,27 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
@@ -6378,27 +6370,27 @@
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K79" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
-        <v>300</v>
+        <v>588</v>
       </c>
       <c r="O79" s="16" t="n">
         <v>0</v>
@@ -6410,32 +6402,32 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G80" s="14" t="inlineStr">
@@ -6445,98 +6437,106 @@
       </c>
       <c r="H80" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J80" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K80" s="14" t="n">
-        <v>12.25</v>
+        <v>0</v>
       </c>
       <c r="L80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M80" s="14" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N80" s="15" t="n">
-        <v>700</v>
-      </c>
-      <c r="O80" s="15" t="n">
-        <v>967.05</v>
+        <v>203.5</v>
+      </c>
+      <c r="O80" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P80" s="15" t="n">
-        <v>78.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31528</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LILLE] - Màj carto</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LILLE</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>Màj carto</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G81" s="11" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J81" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L81" s="11" t="inlineStr"/>
-      <c r="M81" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L81" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-31596</t>
+        </is>
+      </c>
+      <c r="M81" s="11" t="inlineStr">
+        <is>
+          <t>00157967</t>
+        </is>
+      </c>
       <c r="N81" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" s="12" t="n">
+        <v>300</v>
+      </c>
+      <c r="O81" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P81" s="12" t="n">
@@ -6546,27 +6546,27 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F82" s="14" t="inlineStr">
@@ -6586,101 +6586,93 @@
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J82" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K82" s="14" t="n">
-        <v>6.5</v>
+        <v>12.25</v>
       </c>
       <c r="L82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31468</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M82" s="14" t="inlineStr">
         <is>
-          <t>00157346</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N82" s="15" t="n">
-        <v>416.475</v>
-      </c>
-      <c r="O82" s="16" t="n">
-        <v>0</v>
+        <v>700</v>
+      </c>
+      <c r="O82" s="15" t="n">
+        <v>1504.3</v>
       </c>
       <c r="P82" s="15" t="n">
-        <v>0</v>
+        <v>122.8</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31528</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[COMMUNE DE LILLE] - Màj carto</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE LILLE</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Màj carto</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J83" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-31360</t>
-        </is>
-      </c>
-      <c r="M83" s="11" t="inlineStr">
-        <is>
-          <t>00157041</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L83" s="11" t="inlineStr"/>
+      <c r="M83" s="11" t="inlineStr"/>
       <c r="N83" s="12" t="n">
-        <v>210</v>
-      </c>
-      <c r="O83" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P83" s="12" t="n">
@@ -6690,32 +6682,32 @@
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31319</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C84" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LARMOR PLAGE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E84" s="14" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F84" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G84" s="14" t="inlineStr">
@@ -6725,32 +6717,32 @@
       </c>
       <c r="H84" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J84" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K84" s="14" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31328</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M84" s="14" t="inlineStr">
         <is>
-          <t>00156518</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N84" s="15" t="n">
-        <v>281</v>
+        <v>416.475</v>
       </c>
       <c r="O84" s="16" t="n">
         <v>0</v>
@@ -6762,12 +6754,12 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
@@ -6777,12 +6769,12 @@
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
@@ -6802,7 +6794,7 @@
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J85" s="11" t="n">
@@ -6813,16 +6805,16 @@
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N85" s="12" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="O85" s="16" t="n">
         <v>0</v>
@@ -6834,12 +6826,12 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31319</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C86" s="14" t="inlineStr">
@@ -6849,12 +6841,12 @@
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE DE LARMOR PLAGE</t>
         </is>
       </c>
       <c r="E86" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F86" s="14" t="inlineStr">
@@ -6874,7 +6866,7 @@
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J86" s="14" t="n">
@@ -6885,16 +6877,16 @@
       </c>
       <c r="L86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31328</t>
         </is>
       </c>
       <c r="M86" s="14" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156518</t>
         </is>
       </c>
       <c r="N86" s="15" t="n">
-        <v>255</v>
+        <v>281</v>
       </c>
       <c r="O86" s="16" t="n">
         <v>0</v>
@@ -6906,12 +6898,12 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30358</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
@@ -6921,12 +6913,12 @@
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARGELES-SUR-MER</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
@@ -6946,29 +6938,29 @@
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J87" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30366</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
-          <t>00154569</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N87" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O87" s="12" t="n">
+        <v>130</v>
+      </c>
+      <c r="O87" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P87" s="12" t="n">
@@ -6978,12 +6970,12 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C88" s="14" t="inlineStr">
@@ -6993,12 +6985,12 @@
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E88" s="14" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F88" s="14" t="inlineStr">
@@ -7018,27 +7010,27 @@
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J88" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K88" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M88" s="14" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N88" s="15" t="n">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="O88" s="16" t="n">
         <v>0</v>
@@ -7050,32 +7042,32 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30358</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE D'ARGELES-SUR-MER</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G89" s="11" t="inlineStr">
@@ -7085,34 +7077,34 @@
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="J89" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>8.75</v>
+        <v>1.5</v>
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30366</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154569</t>
         </is>
       </c>
       <c r="N89" s="12" t="n">
-        <v>690</v>
-      </c>
-      <c r="O89" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P89" s="12" t="n">
@@ -7122,69 +7114,69 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30044</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>[CD 29] - Commande du flux WFS COM pour Inforoute</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C90" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>CD29</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E90" s="14" t="inlineStr">
         <is>
-          <t>Commande du flux WFS COM pour Inforoute</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F90" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G90" s="14" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H90" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J90" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K90" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30046</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M90" s="14" t="inlineStr">
         <is>
-          <t>00153621</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N90" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" s="15" t="n">
+        <v>140</v>
+      </c>
+      <c r="O90" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P90" s="15" t="n">
@@ -7194,27 +7186,27 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr">
@@ -7234,29 +7226,29 @@
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J91" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K91" s="11" t="n">
-        <v>2.42</v>
+        <v>8.75</v>
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M91" s="11" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N91" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" s="12" t="n">
+        <v>690</v>
+      </c>
+      <c r="O91" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P91" s="12" t="n">
@@ -7266,12 +7258,12 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30044</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[CD 29] - Commande du flux WFS COM pour Inforoute</t>
         </is>
       </c>
       <c r="C92" s="14" t="inlineStr">
@@ -7281,12 +7273,12 @@
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>CD29</t>
         </is>
       </c>
       <c r="E92" s="14" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Commande du flux WFS COM pour Inforoute</t>
         </is>
       </c>
       <c r="F92" s="14" t="inlineStr">
@@ -7296,7 +7288,7 @@
       </c>
       <c r="G92" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H92" s="14" t="inlineStr">
@@ -7306,29 +7298,29 @@
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="J92" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K92" s="14" t="n">
-        <v>2.42</v>
+        <v>1</v>
       </c>
       <c r="L92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30046</t>
         </is>
       </c>
       <c r="M92" s="14" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00153621</t>
         </is>
       </c>
       <c r="N92" s="15" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="O92" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P92" s="15" t="n">
@@ -7389,18 +7381,18 @@
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M93" s="11" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N93" s="12" t="n">
-        <v>787.5</v>
-      </c>
-      <c r="O93" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P93" s="12" t="n">
@@ -7410,26 +7402,28 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29012</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C94" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE</t>
-        </is>
-      </c>
-      <c r="E94" s="14" t="n">
-        <v/>
+          <t>COMMUNE DE BIARRITZ</t>
+        </is>
+      </c>
+      <c r="E94" s="14" t="inlineStr">
+        <is>
+          <t>Paramétrages complémentaires + Vision</t>
+        </is>
       </c>
       <c r="F94" s="14" t="inlineStr">
         <is>
@@ -7448,29 +7442,29 @@
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J94" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K94" s="14" t="n">
-        <v>0.5</v>
+        <v>2.42</v>
       </c>
       <c r="L94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29014</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M94" s="14" t="inlineStr">
         <is>
-          <t>00147236</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N94" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O94" s="15" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="O94" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P94" s="15" t="n">
@@ -7480,32 +7474,32 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G95" s="11" t="inlineStr">
@@ -7515,32 +7509,32 @@
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J95" s="11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K95" s="11" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M95" s="11" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N95" s="12" t="n">
-        <v>725</v>
+        <v>787.5</v>
       </c>
       <c r="O95" s="16" t="n">
         <v>0</v>
@@ -7552,12 +7546,12 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-29012</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
         </is>
       </c>
       <c r="C96" s="14" t="inlineStr">
@@ -7567,7 +7561,7 @@
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
+          <t>COMMUNE DE CARCASSONNE</t>
         </is>
       </c>
       <c r="E96" s="14" t="n">
@@ -7585,28 +7579,28 @@
       </c>
       <c r="H96" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="J96" s="14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K96" s="14" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-29014</t>
         </is>
       </c>
       <c r="M96" s="14" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00147236</t>
         </is>
       </c>
       <c r="N96" s="15" t="n">
@@ -7622,32 +7616,32 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>Commune de CLAMART</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Migration V2</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G97" s="11" t="inlineStr">
@@ -7657,34 +7651,34 @@
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J97" s="11" t="n">
         <v>9</v>
       </c>
       <c r="K97" s="11" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N97" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O97" s="12" t="n">
+        <v>725</v>
+      </c>
+      <c r="O97" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P97" s="12" t="n">
@@ -7694,12 +7688,12 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C98" s="14" t="inlineStr">
@@ -7709,13 +7703,11 @@
       </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E98" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E98" s="14" t="n">
+        <v/>
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
@@ -7734,23 +7726,23 @@
       </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J98" s="14" t="n">
         <v>9</v>
       </c>
       <c r="K98" s="14" t="n">
-        <v>0.85</v>
+        <v>2</v>
       </c>
       <c r="L98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M98" s="14" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N98" s="15" t="n">
@@ -7817,12 +7809,12 @@
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M99" s="11" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N99" s="12" t="n">
@@ -7889,12 +7881,12 @@
       </c>
       <c r="L100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M100" s="14" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N100" s="15" t="n">
@@ -7961,18 +7953,18 @@
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N101" s="12" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O101" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P101" s="12" t="n">
@@ -7982,12 +7974,12 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C102" s="14" t="inlineStr">
@@ -7997,11 +7989,13 @@
       </c>
       <c r="D102" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E102" s="14" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E102" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
@@ -8015,28 +8009,28 @@
       </c>
       <c r="H102" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I102" s="14" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J102" s="14" t="n">
         <v>9</v>
       </c>
       <c r="K102" s="14" t="n">
-        <v>1.25</v>
+        <v>0.85</v>
       </c>
       <c r="L102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M102" s="14" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N102" s="15" t="n">
@@ -8052,12 +8046,12 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
@@ -8067,11 +8061,13 @@
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
-        </is>
-      </c>
-      <c r="E103" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E103" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
         <is>
@@ -8090,29 +8086,29 @@
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J103" s="11" t="n">
         <v>9</v>
       </c>
       <c r="K103" s="11" t="n">
-        <v>8.25</v>
+        <v>0.85</v>
       </c>
       <c r="L103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M103" s="11" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N103" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O103" s="12" t="n">
+        <v>1320</v>
+      </c>
+      <c r="O103" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P103" s="12" t="n">
@@ -8122,12 +8118,12 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C104" s="14" t="inlineStr">
@@ -8137,7 +8133,7 @@
       </c>
       <c r="D104" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
         </is>
       </c>
       <c r="E104" s="14" t="n">
@@ -8155,34 +8151,34 @@
       </c>
       <c r="H104" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J104" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K104" s="14" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="L104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-27642</t>
         </is>
       </c>
       <c r="M104" s="14" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00143935</t>
         </is>
       </c>
       <c r="N104" s="15" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O104" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P104" s="15" t="n">
@@ -8192,28 +8188,26 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24774</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>[SETE] - LITTERALIS</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
-        </is>
-      </c>
-      <c r="E105" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
+        </is>
+      </c>
+      <c r="E105" s="11" t="n">
+        <v/>
       </c>
       <c r="F105" s="11" t="inlineStr">
         <is>
@@ -8232,23 +8226,23 @@
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J105" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>0.25</v>
+        <v>8.25</v>
       </c>
       <c r="L105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27578</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M105" s="11" t="inlineStr">
         <is>
-          <t>499043</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N105" s="12" t="n">
@@ -8264,12 +8258,12 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24216</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>MMM - LITTERALIS Script purge de données</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C106" s="14" t="inlineStr">
@@ -8279,13 +8273,11 @@
       </c>
       <c r="D106" s="14" t="inlineStr">
         <is>
-          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
-        </is>
-      </c>
-      <c r="E106" s="14" t="inlineStr">
-        <is>
-          <t>Script purge de données</t>
-        </is>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+        </is>
+      </c>
+      <c r="E106" s="14" t="n">
+        <v/>
       </c>
       <c r="F106" s="14" t="inlineStr">
         <is>
@@ -8294,31 +8286,39 @@
       </c>
       <c r="G106" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H106" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I106" s="14" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J106" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K106" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L106" s="14" t="inlineStr"/>
-      <c r="M106" s="14" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L106" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27017</t>
+        </is>
+      </c>
+      <c r="M106" s="14" t="inlineStr">
+        <is>
+          <t>00141205</t>
+        </is>
+      </c>
       <c r="N106" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O106" s="15" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O106" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P106" s="15" t="n">
@@ -8328,12 +8328,12 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24774</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>[SETE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
@@ -8343,11 +8343,13 @@
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
-        </is>
-      </c>
-      <c r="E107" s="11" t="n">
-        <v/>
+          <t>COMMUNE DE SETE</t>
+        </is>
+      </c>
+      <c r="E107" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F107" s="11" t="inlineStr">
         <is>
@@ -8366,23 +8368,23 @@
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J107" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K107" s="11" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27996</t>
+          <t>PDMDEP-27578</t>
         </is>
       </c>
       <c r="M107" s="11" t="inlineStr">
         <is>
-          <t>501219</t>
+          <t>499043</t>
         </is>
       </c>
       <c r="N107" s="12" t="n">
@@ -8398,26 +8400,28 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24216</t>
         </is>
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>MMM - LITTERALIS Script purge de données</t>
         </is>
       </c>
       <c r="C108" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D108" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
-        </is>
-      </c>
-      <c r="E108" s="14" t="n">
-        <v/>
+          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
+        </is>
+      </c>
+      <c r="E108" s="14" t="inlineStr">
+        <is>
+          <t>Script purge de données</t>
+        </is>
       </c>
       <c r="F108" s="14" t="inlineStr">
         <is>
@@ -8426,35 +8430,27 @@
       </c>
       <c r="G108" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H108" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="J108" s="14" t="n">
         <v>11</v>
       </c>
       <c r="K108" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L108" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27995</t>
-        </is>
-      </c>
-      <c r="M108" s="14" t="inlineStr">
-        <is>
-          <t>501218</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L108" s="14" t="inlineStr"/>
+      <c r="M108" s="14" t="inlineStr"/>
       <c r="N108" s="15" t="n">
         <v>0</v>
       </c>
@@ -8468,22 +8464,22 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E109" s="11" t="n">
@@ -8506,23 +8502,23 @@
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J109" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K109" s="11" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="L109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M109" s="11" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N109" s="12" t="n">
@@ -8538,22 +8534,22 @@
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C110" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D110" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E110" s="14" t="n">
@@ -8576,23 +8572,23 @@
       </c>
       <c r="I110" s="14" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J110" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K110" s="14" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M110" s="14" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N110" s="15" t="n">
@@ -8608,12 +8604,12 @@
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
@@ -8623,7 +8619,7 @@
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E111" s="11" t="n">
@@ -8646,23 +8642,23 @@
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J111" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K111" s="11" t="n">
-        <v>1.31</v>
+        <v>3</v>
       </c>
       <c r="L111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M111" s="11" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N111" s="12" t="n">
@@ -8678,12 +8674,12 @@
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C112" s="14" t="inlineStr">
@@ -8693,7 +8689,7 @@
       </c>
       <c r="D112" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E112" s="14" t="n">
@@ -8716,23 +8712,23 @@
       </c>
       <c r="I112" s="14" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J112" s="14" t="n">
         <v>13</v>
       </c>
       <c r="K112" s="14" t="n">
-        <v>1.31</v>
+        <v>0.25</v>
       </c>
       <c r="L112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M112" s="14" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N112" s="15" t="n">
@@ -8763,7 +8759,7 @@
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E113" s="11" t="n">
@@ -8797,12 +8793,12 @@
       </c>
       <c r="L113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M113" s="11" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N113" s="12" t="n">
@@ -8867,12 +8863,12 @@
       </c>
       <c r="L114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M114" s="14" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N114" s="15" t="n">
@@ -8888,22 +8884,22 @@
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E115" s="11" t="n">
@@ -8921,34 +8917,34 @@
       </c>
       <c r="H115" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I115" s="11" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J115" s="11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K115" s="11" t="n">
-        <v>0.5</v>
+        <v>1.31</v>
       </c>
       <c r="L115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M115" s="11" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N115" s="12" t="n">
-        <v>401</v>
-      </c>
-      <c r="O115" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P115" s="12" t="n">
@@ -8958,12 +8954,12 @@
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21249</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B116" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C116" s="14" t="inlineStr">
@@ -8973,7 +8969,7 @@
       </c>
       <c r="D116" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E116" s="14" t="n">
@@ -8989,20 +8985,32 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H116" s="14" t="inlineStr"/>
+      <c r="H116" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I116" s="14" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J116" s="14" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K116" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L116" s="14" t="inlineStr"/>
-      <c r="M116" s="14" t="inlineStr"/>
+        <v>1.31</v>
+      </c>
+      <c r="L116" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27365</t>
+        </is>
+      </c>
+      <c r="M116" s="14" t="inlineStr">
+        <is>
+          <t>491593</t>
+        </is>
+      </c>
       <c r="N116" s="15" t="n">
         <v>0</v>
       </c>
@@ -9016,12 +9024,12 @@
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
@@ -9031,7 +9039,7 @@
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E117" s="11" t="n">
@@ -9049,34 +9057,34 @@
       </c>
       <c r="H117" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I117" s="11" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J117" s="11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K117" s="11" t="n">
-        <v>7</v>
+        <v>0.5</v>
       </c>
       <c r="L117" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M117" s="11" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N117" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O117" s="12" t="n">
+        <v>401</v>
+      </c>
+      <c r="O117" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P117" s="12" t="n">
@@ -9086,12 +9094,12 @@
     <row r="118">
       <c r="A118" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-21249</t>
         </is>
       </c>
       <c r="B118" s="14" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="C118" s="14" t="inlineStr">
@@ -9101,7 +9109,7 @@
       </c>
       <c r="D118" s="14" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="E118" s="14" t="n">
@@ -9117,14 +9125,10 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H118" s="14" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+      <c r="H118" s="14" t="inlineStr"/>
       <c r="I118" s="14" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J118" s="14" t="n">
@@ -9133,16 +9137,8 @@
       <c r="K118" s="14" t="n">
         <v>0.5</v>
       </c>
-      <c r="L118" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28035</t>
-        </is>
-      </c>
-      <c r="M118" s="14" t="inlineStr">
-        <is>
-          <t>468660</t>
-        </is>
-      </c>
+      <c r="L118" s="14" t="inlineStr"/>
+      <c r="M118" s="14" t="inlineStr"/>
       <c r="N118" s="15" t="n">
         <v>0</v>
       </c>
@@ -9156,12 +9152,12 @@
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
@@ -9171,7 +9167,7 @@
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E119" s="11" t="n">
@@ -9189,34 +9185,34 @@
       </c>
       <c r="H119" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I119" s="11" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J119" s="11" t="n">
         <v>16</v>
       </c>
       <c r="K119" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L119" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M119" s="11" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N119" s="12" t="n">
-        <v>230</v>
-      </c>
-      <c r="O119" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P119" s="12" t="n">
@@ -9226,12 +9222,12 @@
     <row r="120">
       <c r="A120" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B120" s="14" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C120" s="14" t="inlineStr">
@@ -9241,7 +9237,7 @@
       </c>
       <c r="D120" s="14" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E120" s="14" t="n">
@@ -9254,23 +9250,35 @@
       </c>
       <c r="G120" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H120" s="14" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H120" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I120" s="14" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J120" s="14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K120" s="14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L120" s="14" t="inlineStr"/>
-      <c r="M120" s="14" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L120" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28035</t>
+        </is>
+      </c>
+      <c r="M120" s="14" t="inlineStr">
+        <is>
+          <t>468660</t>
+        </is>
+      </c>
       <c r="N120" s="15" t="n">
         <v>0</v>
       </c>
@@ -9284,12 +9292,12 @@
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
@@ -9299,7 +9307,7 @@
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E121" s="11" t="n">
@@ -9317,34 +9325,34 @@
       </c>
       <c r="H121" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I121" s="11" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J121" s="11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K121" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L121" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28027</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M121" s="11" t="inlineStr">
         <is>
-          <t>470688</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N121" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O121" s="12" t="n">
+        <v>230</v>
+      </c>
+      <c r="O121" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P121" s="12" t="n">
@@ -9354,22 +9362,22 @@
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B122" s="14" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C122" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D122" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E122" s="14" t="n">
@@ -9382,35 +9390,23 @@
       </c>
       <c r="G122" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H122" s="14" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H122" s="14" t="inlineStr"/>
       <c r="I122" s="14" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J122" s="14" t="n">
         <v>17</v>
       </c>
       <c r="K122" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L122" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27568</t>
-        </is>
-      </c>
-      <c r="M122" s="14" t="inlineStr">
-        <is>
-          <t>471958</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L122" s="14" t="inlineStr"/>
+      <c r="M122" s="14" t="inlineStr"/>
       <c r="N122" s="15" t="n">
         <v>0</v>
       </c>
@@ -9424,12 +9420,12 @@
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
@@ -9439,7 +9435,7 @@
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E123" s="11" t="n">
@@ -9452,7 +9448,7 @@
       </c>
       <c r="G123" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H123" s="11" t="inlineStr">
@@ -9462,17 +9458,25 @@
       </c>
       <c r="I123" s="11" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J123" s="11" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="L123" s="11" t="inlineStr"/>
-      <c r="M123" s="11" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L123" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28027</t>
+        </is>
+      </c>
+      <c r="M123" s="11" t="inlineStr">
+        <is>
+          <t>470688</t>
+        </is>
+      </c>
       <c r="N123" s="12" t="n">
         <v>0</v>
       </c>
@@ -9486,12 +9490,12 @@
     <row r="124">
       <c r="A124" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18196</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B124" s="14" t="inlineStr">
         <is>
-          <t>[GENTILLY] - Litteralis Expert SAAS</t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C124" s="14" t="inlineStr">
@@ -9501,7 +9505,7 @@
       </c>
       <c r="D124" s="14" t="inlineStr">
         <is>
-          <t>Gentilly</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E124" s="14" t="n">
@@ -9514,27 +9518,35 @@
       </c>
       <c r="G124" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H124" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I124" s="14" t="inlineStr">
         <is>
-          <t>19/12/2024</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J124" s="14" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K124" s="14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L124" s="14" t="inlineStr"/>
-      <c r="M124" s="14" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L124" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27568</t>
+        </is>
+      </c>
+      <c r="M124" s="14" t="inlineStr">
+        <is>
+          <t>471958</t>
+        </is>
+      </c>
       <c r="N124" s="15" t="n">
         <v>0</v>
       </c>
@@ -9548,22 +9560,22 @@
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E125" s="11" t="n">
@@ -9571,44 +9583,36 @@
       </c>
       <c r="F125" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G125" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H125" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I125" s="11" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J125" s="11" t="n">
         <v>20</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L125" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M125" s="11" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="L125" s="11" t="inlineStr"/>
+      <c r="M125" s="11" t="inlineStr"/>
       <c r="N125" s="12" t="n">
-        <v>240</v>
-      </c>
-      <c r="O125" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P125" s="12" t="n">
@@ -9618,12 +9622,12 @@
     <row r="126">
       <c r="A126" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18196</t>
         </is>
       </c>
       <c r="B126" s="14" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[GENTILLY] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C126" s="14" t="inlineStr">
@@ -9633,7 +9637,7 @@
       </c>
       <c r="D126" s="14" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>Gentilly</t>
         </is>
       </c>
       <c r="E126" s="14" t="n">
@@ -9646,39 +9650,31 @@
       </c>
       <c r="G126" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H126" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I126" s="14" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>19/12/2024</t>
         </is>
       </c>
       <c r="J126" s="14" t="n">
         <v>20</v>
       </c>
       <c r="K126" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L126" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28023</t>
-        </is>
-      </c>
-      <c r="M126" s="14" t="inlineStr">
-        <is>
-          <t>454387</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L126" s="14" t="inlineStr"/>
+      <c r="M126" s="14" t="inlineStr"/>
       <c r="N126" s="15" t="n">
-        <v>557.145</v>
-      </c>
-      <c r="O126" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P126" s="15" t="n">
@@ -9688,22 +9684,22 @@
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E127" s="11" t="n">
@@ -9711,36 +9707,44 @@
       </c>
       <c r="F127" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G127" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H127" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I127" s="11" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J127" s="11" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K127" s="11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L127" s="11" t="inlineStr"/>
-      <c r="M127" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L127" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M127" s="11" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
       <c r="N127" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O127" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="O127" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P127" s="12" t="n">
@@ -9750,12 +9754,12 @@
     <row r="128">
       <c r="A128" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-14798</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B128" s="14" t="inlineStr">
         <is>
-          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C128" s="14" t="inlineStr">
@@ -9765,7 +9769,7 @@
       </c>
       <c r="D128" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E128" s="14" t="n">
@@ -9778,7 +9782,7 @@
       </c>
       <c r="G128" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H128" s="14" t="inlineStr">
@@ -9788,29 +9792,29 @@
       </c>
       <c r="I128" s="14" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J128" s="14" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K128" s="14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L128" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28003</t>
+          <t>PDMDEP-28023</t>
         </is>
       </c>
       <c r="M128" s="14" t="inlineStr">
         <is>
-          <t>412981</t>
+          <t>454387</t>
         </is>
       </c>
       <c r="N128" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O128" s="15" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O128" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P128" s="15" t="n">
@@ -9820,12 +9824,12 @@
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-14118</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>[SURESNES] Interface FAST-Parapheur</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
@@ -9835,7 +9839,7 @@
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>Suresnes</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E129" s="11" t="n">
@@ -9858,14 +9862,14 @@
       </c>
       <c r="I129" s="11" t="inlineStr">
         <is>
-          <t>01/02/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J129" s="11" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="K129" s="11" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="L129" s="11" t="inlineStr"/>
       <c r="M129" s="11" t="inlineStr"/>
@@ -9882,12 +9886,12 @@
     <row r="130">
       <c r="A130" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-14798</t>
         </is>
       </c>
       <c r="B130" s="14" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
         </is>
       </c>
       <c r="C130" s="14" t="inlineStr">
@@ -9897,7 +9901,7 @@
       </c>
       <c r="D130" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
         </is>
       </c>
       <c r="E130" s="14" t="n">
@@ -9920,17 +9924,25 @@
       </c>
       <c r="I130" s="14" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>05/04/2024</t>
         </is>
       </c>
       <c r="J130" s="14" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K130" s="14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L130" s="14" t="inlineStr"/>
-      <c r="M130" s="14" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="L130" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28003</t>
+        </is>
+      </c>
+      <c r="M130" s="14" t="inlineStr">
+        <is>
+          <t>412981</t>
+        </is>
+      </c>
       <c r="N130" s="15" t="n">
         <v>0</v>
       </c>
@@ -9944,22 +9956,22 @@
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-14118</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[SURESNES] Interface FAST-Parapheur</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>Suresnes</t>
         </is>
       </c>
       <c r="E131" s="11" t="n">
@@ -9972,7 +9984,7 @@
       </c>
       <c r="G131" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H131" s="11" t="inlineStr">
@@ -9982,25 +9994,17 @@
       </c>
       <c r="I131" s="11" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>01/02/2024</t>
         </is>
       </c>
       <c r="J131" s="11" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K131" s="11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L131" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M131" s="11" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L131" s="11" t="inlineStr"/>
+      <c r="M131" s="11" t="inlineStr"/>
       <c r="N131" s="12" t="n">
         <v>0</v>
       </c>
@@ -10014,22 +10018,22 @@
     <row r="132">
       <c r="A132" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B132" s="14" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C132" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D132" s="14" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E132" s="14" t="n">
@@ -10045,17 +10049,21 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H132" s="14" t="inlineStr"/>
+      <c r="H132" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I132" s="14" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J132" s="14" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K132" s="14" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="L132" s="14" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -10072,22 +10080,22 @@
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E133" s="11" t="n">
@@ -10100,33 +10108,33 @@
       </c>
       <c r="G133" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H133" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I133" s="11" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J133" s="11" t="n">
         <v>35</v>
       </c>
       <c r="K133" s="11" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="L133" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34532</t>
+          <t>PDMDEP-27990</t>
         </is>
       </c>
       <c r="M133" s="11" t="inlineStr">
         <is>
-          <t>412263</t>
+          <t>406296</t>
         </is>
       </c>
       <c r="N133" s="12" t="n">
@@ -10142,12 +10150,12 @@
     <row r="134">
       <c r="A134" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12443</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B134" s="14" t="inlineStr">
         <is>
-          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C134" s="14" t="inlineStr">
@@ -10157,7 +10165,7 @@
       </c>
       <c r="D134" s="14" t="inlineStr">
         <is>
-          <t>CD79 - Deux Sèvres</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E134" s="14" t="n">
@@ -10173,14 +10181,10 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H134" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H134" s="14" t="inlineStr"/>
       <c r="I134" s="14" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J134" s="14" t="n">
@@ -10204,28 +10208,26 @@
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E135" s="11" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>LE MANS METROPOLE</t>
+        </is>
+      </c>
+      <c r="E135" s="11" t="n">
+        <v/>
       </c>
       <c r="F135" s="11" t="inlineStr">
         <is>
@@ -10239,22 +10241,30 @@
       </c>
       <c r="H135" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I135" s="11" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J135" s="11" t="n">
         <v>35</v>
       </c>
       <c r="K135" s="11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L135" s="11" t="inlineStr"/>
-      <c r="M135" s="11" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L135" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M135" s="11" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N135" s="12" t="n">
         <v>0</v>
       </c>
@@ -10268,24 +10278,26 @@
     <row r="136">
       <c r="A136" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12443</t>
         </is>
       </c>
       <c r="B136" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C136" s="14" t="inlineStr"/>
+          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C136" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D136" s="14" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E136" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>CD79 - Deux Sèvres</t>
+        </is>
+      </c>
+      <c r="E136" s="14" t="n">
+        <v/>
       </c>
       <c r="F136" s="14" t="inlineStr">
         <is>
@@ -10304,14 +10316,14 @@
       </c>
       <c r="I136" s="14" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J136" s="14" t="n">
         <v>35</v>
       </c>
       <c r="K136" s="14" t="n">
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="L136" s="14" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -10328,27 +10340,27 @@
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-2155</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
+          <t>[CD 14] Paramétrages</t>
         </is>
       </c>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>CD14</t>
         </is>
       </c>
       <c r="E137" s="11" t="inlineStr">
         <is>
-          <t>Montée de version + Pastell</t>
+          <t>Modélisation spécifique</t>
         </is>
       </c>
       <c r="F137" s="11" t="inlineStr">
@@ -10368,14 +10380,14 @@
       </c>
       <c r="I137" s="11" t="inlineStr">
         <is>
-          <t>02/08/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J137" s="11" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K137" s="11" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="L137" s="11" t="inlineStr"/>
       <c r="M137" s="11" t="inlineStr"/>
@@ -10392,21 +10404,25 @@
     <row r="138">
       <c r="A138" s="13" t="inlineStr">
         <is>
-          <t>PSC-1326</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B138" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C138" s="14" t="inlineStr"/>
       <c r="D138" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
-        </is>
-      </c>
-      <c r="E138" s="14" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E138" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F138" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -10414,20 +10430,24 @@
       </c>
       <c r="G138" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H138" s="14" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H138" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I138" s="14" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J138" s="14" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="K138" s="14" t="n">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="L138" s="14" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -10444,21 +10464,29 @@
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>PSC-1320</t>
+          <t>PDMDEP-2155</t>
         </is>
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
-        </is>
-      </c>
-      <c r="C139" s="11" t="inlineStr"/>
+          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
+        </is>
+      </c>
+      <c r="C139" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D139" s="11" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
-        </is>
-      </c>
-      <c r="E139" s="11" t="inlineStr"/>
+          <t>COMMUNE DE CHAMBERY</t>
+        </is>
+      </c>
+      <c r="E139" s="11" t="inlineStr">
+        <is>
+          <t>Montée de version + Pastell</t>
+        </is>
+      </c>
       <c r="F139" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -10466,20 +10494,24 @@
       </c>
       <c r="G139" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H139" s="11" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H139" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I139" s="11" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>02/08/2023</t>
         </is>
       </c>
       <c r="J139" s="11" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="K139" s="11" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L139" s="11" t="inlineStr"/>
       <c r="M139" s="11" t="inlineStr"/>
@@ -10496,18 +10528,18 @@
     <row r="140">
       <c r="A140" s="13" t="inlineStr">
         <is>
-          <t>PSC-850</t>
+          <t>PSC-1326</t>
         </is>
       </c>
       <c r="B140" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="C140" s="14" t="inlineStr"/>
       <c r="D140" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="E140" s="14" t="inlineStr"/>
@@ -10524,14 +10556,14 @@
       <c r="H140" s="14" t="inlineStr"/>
       <c r="I140" s="14" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J140" s="14" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K140" s="14" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L140" s="14" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -10548,18 +10580,18 @@
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>PSC-583</t>
+          <t>PSC-1320</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>Cournonsec</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="C141" s="11" t="inlineStr"/>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t>Cournonsec</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="E141" s="11" t="inlineStr"/>
@@ -10576,11 +10608,11 @@
       <c r="H141" s="11" t="inlineStr"/>
       <c r="I141" s="11" t="inlineStr">
         <is>
-          <t>20/03/2025</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J141" s="11" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="K141" s="11" t="n">
         <v>0.25</v>
@@ -10598,31 +10630,135 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="17" t="inlineStr">
+      <c r="A142" s="13" t="inlineStr">
+        <is>
+          <t>PSC-850</t>
+        </is>
+      </c>
+      <c r="B142" s="14" t="inlineStr">
+        <is>
+          <t>MAIRIE MARINGUES</t>
+        </is>
+      </c>
+      <c r="C142" s="14" t="inlineStr"/>
+      <c r="D142" s="14" t="inlineStr">
+        <is>
+          <t>MAIRIE MARINGUES</t>
+        </is>
+      </c>
+      <c r="E142" s="14" t="inlineStr"/>
+      <c r="F142" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G142" s="14" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H142" s="14" t="inlineStr"/>
+      <c r="I142" s="14" t="inlineStr">
+        <is>
+          <t>10/06/2025</t>
+        </is>
+      </c>
+      <c r="J142" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="K142" s="14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L142" s="14" t="inlineStr"/>
+      <c r="M142" s="14" t="inlineStr"/>
+      <c r="N142" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="10" t="inlineStr">
+        <is>
+          <t>PSC-583</t>
+        </is>
+      </c>
+      <c r="B143" s="11" t="inlineStr">
+        <is>
+          <t>Cournonsec</t>
+        </is>
+      </c>
+      <c r="C143" s="11" t="inlineStr"/>
+      <c r="D143" s="11" t="inlineStr">
+        <is>
+          <t>Cournonsec</t>
+        </is>
+      </c>
+      <c r="E143" s="11" t="inlineStr"/>
+      <c r="F143" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G143" s="11" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H143" s="11" t="inlineStr"/>
+      <c r="I143" s="11" t="inlineStr">
+        <is>
+          <t>20/03/2025</t>
+        </is>
+      </c>
+      <c r="J143" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="K143" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L143" s="11" t="inlineStr"/>
+      <c r="M143" s="11" t="inlineStr"/>
+      <c r="N143" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P143" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B142" s="17" t="inlineStr"/>
-      <c r="C142" s="17" t="inlineStr"/>
-      <c r="D142" s="17" t="inlineStr"/>
-      <c r="E142" s="17" t="inlineStr"/>
-      <c r="F142" s="17" t="inlineStr"/>
-      <c r="G142" s="17" t="inlineStr"/>
-      <c r="H142" s="17" t="inlineStr"/>
-      <c r="I142" s="17" t="inlineStr"/>
-      <c r="J142" s="17" t="inlineStr"/>
-      <c r="K142" s="17" t="inlineStr"/>
-      <c r="L142" s="17" t="inlineStr"/>
-      <c r="M142" s="17" t="inlineStr"/>
-      <c r="N142" s="18" t="n">
-        <v>66066.194</v>
-      </c>
-      <c r="O142" s="18" t="n">
-        <v>16406.71</v>
-      </c>
-      <c r="P142" s="18" t="n">
-        <v>79.83</v>
+      <c r="B144" s="17" t="inlineStr"/>
+      <c r="C144" s="17" t="inlineStr"/>
+      <c r="D144" s="17" t="inlineStr"/>
+      <c r="E144" s="17" t="inlineStr"/>
+      <c r="F144" s="17" t="inlineStr"/>
+      <c r="G144" s="17" t="inlineStr"/>
+      <c r="H144" s="17" t="inlineStr"/>
+      <c r="I144" s="17" t="inlineStr"/>
+      <c r="J144" s="17" t="inlineStr"/>
+      <c r="K144" s="17" t="inlineStr"/>
+      <c r="L144" s="17" t="inlineStr"/>
+      <c r="M144" s="17" t="inlineStr"/>
+      <c r="N144" s="18" t="n">
+        <v>64017.394</v>
+      </c>
+      <c r="O144" s="18" t="n">
+        <v>21098.53</v>
+      </c>
+      <c r="P144" s="18" t="n">
+        <v>101.92</v>
       </c>
     </row>
   </sheetData>
@@ -10765,6 +10901,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId135"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId139"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10776,13 +10914,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="47" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
@@ -10802,7 +10940,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tickets 'Matériel GEODP' clôturés ce mois — 1 ligne(s)</t>
+          <t>Tickets 'Matériel GEODP' clôturés ce mois — 2 ligne(s)</t>
         </is>
       </c>
     </row>
@@ -10918,28 +11056,82 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-33638</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>[COMMUNE DE MOULINS] - Migration GEODP Placier + Acquisition module Caisse</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE MOULINS</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>Migration GeODP Placier et MEP module Caisse</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-33645</t>
+        </is>
+      </c>
+      <c r="J6" s="14" t="inlineStr">
+        <is>
+          <t>00169250</t>
+        </is>
+      </c>
+      <c r="K6" s="15" t="n">
+        <v>2445</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr"/>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr"/>
-      <c r="E6" s="17" t="inlineStr"/>
-      <c r="F6" s="17" t="inlineStr"/>
-      <c r="G6" s="17" t="inlineStr"/>
-      <c r="H6" s="17" t="inlineStr"/>
-      <c r="I6" s="17" t="inlineStr"/>
-      <c r="J6" s="17" t="inlineStr"/>
-      <c r="K6" s="18" t="n">
-        <v>450</v>
+      <c r="B7" s="17" t="inlineStr"/>
+      <c r="C7" s="17" t="inlineStr"/>
+      <c r="D7" s="17" t="inlineStr"/>
+      <c r="E7" s="17" t="inlineStr"/>
+      <c r="F7" s="17" t="inlineStr"/>
+      <c r="G7" s="17" t="inlineStr"/>
+      <c r="H7" s="17" t="inlineStr"/>
+      <c r="I7" s="17" t="inlineStr"/>
+      <c r="J7" s="17" t="inlineStr"/>
+      <c r="K7" s="18" t="n">
+        <v>2895</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:K4"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11420,10 +11612,10 @@
         <v>29.5</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>189.75</v>
+        <v>191.25</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>66.25</v>
@@ -11433,7 +11625,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>31.8%</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11667,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>105.5</v>
+        <v>106.25</v>
       </c>
     </row>
   </sheetData>
@@ -11560,22 +11752,22 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>380967</v>
+        <v>376276</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>145932</v>
+        <v>143042</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>235035</v>
+        <v>233234</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>148266</v>
+        <v>146689</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>21179</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>26461</v>
+        <v>26236</v>
       </c>
     </row>
     <row r="6">
@@ -11585,22 +11777,22 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>170493</v>
+        <v>168133</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>65841</v>
+        <v>64211</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>104652</v>
+        <v>103922</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>87237</v>
+        <v>86732</v>
       </c>
       <c r="F6" s="25" t="n">
         <v>11307</v>
       </c>
       <c r="G6" s="25" t="n">
-        <v>3508</v>
+        <v>3283</v>
       </c>
     </row>
     <row r="7">
@@ -11610,16 +11802,16 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>210474</v>
+        <v>208143</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>80091</v>
+        <v>78831</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>130383</v>
+        <v>129312</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>61029</v>
+        <v>59957</v>
       </c>
       <c r="F7" s="26" t="n">
         <v>9871</v>
@@ -11639,7 +11831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -11663,7 +11855,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 15 commande(s)</t>
+          <t>Épics créées ce mois — 14 commande(s)</t>
         </is>
       </c>
     </row>
@@ -12303,22 +12495,22 @@
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34970</t>
+          <t>PDMDEP-34929</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34966</t>
+          <t>PDMDEP-34925</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Commune de Villeneuve D'Ascq</t>
+          <t>COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
@@ -12338,62 +12530,38 @@
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>00146508</t>
+          <t>00178034</t>
         </is>
       </c>
       <c r="I18" s="26" t="n">
-        <v>0</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34929</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34925</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="inlineStr">
-        <is>
-          <t>04/08/2026</t>
-        </is>
-      </c>
-      <c r="D19" s="14" t="inlineStr">
-        <is>
-          <t>COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE</t>
-        </is>
-      </c>
-      <c r="E19" s="14" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="F19" s="14" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
-      <c r="G19" s="14" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
-      <c r="H19" s="14" t="inlineStr">
-        <is>
-          <t>00178034</t>
-        </is>
-      </c>
-      <c r="I19" s="25" t="n">
-        <v>2300</v>
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="17" t="n"/>
+      <c r="E19" s="17" t="n"/>
+      <c r="F19" s="17" t="n"/>
+      <c r="G19" s="17" t="n"/>
+      <c r="H19" s="17" t="inlineStr">
+        <is>
+          <t>14 commande(s)</t>
+        </is>
+      </c>
+      <c r="I19" s="24" t="n">
+        <v>19898</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B20" s="17" t="n"/>
@@ -12404,17 +12572,17 @@
       <c r="G20" s="17" t="n"/>
       <c r="H20" s="17" t="inlineStr">
         <is>
-          <t>15 commande(s)</t>
+          <t>5 commande(s)</t>
         </is>
       </c>
       <c r="I20" s="24" t="n">
-        <v>19898</v>
+        <v>7736</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="17" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>dont GEODP</t>
         </is>
       </c>
       <c r="B21" s="17" t="n"/>
@@ -12425,31 +12593,10 @@
       <c r="G21" s="17" t="n"/>
       <c r="H21" s="17" t="inlineStr">
         <is>
-          <t>6 commande(s)</t>
+          <t>9 commande(s)</t>
         </is>
       </c>
       <c r="I21" s="24" t="n">
-        <v>7736</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="17" t="inlineStr">
-        <is>
-          <t>dont GEODP</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="n"/>
-      <c r="C22" s="17" t="n"/>
-      <c r="D22" s="17" t="n"/>
-      <c r="E22" s="17" t="n"/>
-      <c r="F22" s="17" t="n"/>
-      <c r="G22" s="17" t="n"/>
-      <c r="H22" s="17" t="inlineStr">
-        <is>
-          <t>9 commande(s)</t>
-        </is>
-      </c>
-      <c r="I22" s="24" t="n">
         <v>12162</v>
       </c>
     </row>
@@ -12464,7 +12611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -12485,7 +12632,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5 clôture(s) : 5 projet(s), 0 rework</t>
+          <t>6 clôture(s) : 6 projet(s), 0 rework</t>
         </is>
       </c>
     </row>
@@ -12645,59 +12792,89 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
+          <t>PDMDEP-33781</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[COMMUNE DE SAINT DIZIER] - Modélisation de petits éléments </t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE SAINT DIZIER</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
           <t>PDMDEP-34848</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>[COMMUNE DE BRUAY LA BUISSIERE] - Modification en-tête des a</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>COMMUNE DE BRUAY LA BUISSIERE</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n">
+      <c r="F10" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>TOTAL projets clôturés</t>
         </is>
       </c>
-      <c r="B11" s="17" t="n"/>
-      <c r="C11" s="17" t="n"/>
-      <c r="D11" s="17" t="n"/>
-      <c r="E11" s="17" t="n"/>
-      <c r="F11" s="17" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="27" t="inlineStr">
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>TOTAL rework clôturés</t>
         </is>
       </c>
-      <c r="B12" s="27" t="n"/>
-      <c r="C12" s="27" t="n"/>
-      <c r="D12" s="27" t="n"/>
-      <c r="E12" s="27" t="n"/>
-      <c r="F12" s="27" t="n">
+      <c r="B13" s="27" t="n"/>
+      <c r="C13" s="27" t="n"/>
+      <c r="D13" s="27" t="n"/>
+      <c r="E13" s="27" t="n"/>
+      <c r="F13" s="27" t="n">
         <v>0</v>
       </c>
     </row>

--- a/jira_export_2026-08-25.xlsx
+++ b/jira_export_2026-08-25.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>21,099 €</t>
+          <t>21,694 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -760,7 +760,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>8,950 €</t>
+          <t>9,545 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>387 h</t>
+          <t>388 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P144"/>
+  <dimension ref="A1:P145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -3365,7 +3365,7 @@
         <v>2</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
@@ -10632,18 +10632,18 @@
     <row r="142">
       <c r="A142" s="13" t="inlineStr">
         <is>
-          <t>PSC-850</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B142" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C142" s="14" t="inlineStr"/>
       <c r="D142" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E142" s="14" t="inlineStr"/>
@@ -10654,28 +10654,36 @@
       </c>
       <c r="G142" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H142" s="14" t="inlineStr"/>
       <c r="I142" s="14" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J142" s="14" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="K142" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L142" s="14" t="inlineStr"/>
-      <c r="M142" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L142" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M142" s="14" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
       <c r="N142" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O142" s="15" t="n">
-        <v>0</v>
+        <v>595.7</v>
       </c>
       <c r="P142" s="15" t="n">
         <v>0</v>
@@ -10684,18 +10692,18 @@
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>PSC-583</t>
+          <t>PSC-850</t>
         </is>
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>Cournonsec</t>
+          <t>MAIRIE MARINGUES</t>
         </is>
       </c>
       <c r="C143" s="11" t="inlineStr"/>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>Cournonsec</t>
+          <t>MAIRIE MARINGUES</t>
         </is>
       </c>
       <c r="E143" s="11" t="inlineStr"/>
@@ -10712,11 +10720,11 @@
       <c r="H143" s="11" t="inlineStr"/>
       <c r="I143" s="11" t="inlineStr">
         <is>
-          <t>20/03/2025</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="J143" s="11" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K143" s="11" t="n">
         <v>0.25</v>
@@ -10734,31 +10742,83 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="17" t="inlineStr">
+      <c r="A144" s="13" t="inlineStr">
+        <is>
+          <t>PSC-583</t>
+        </is>
+      </c>
+      <c r="B144" s="14" t="inlineStr">
+        <is>
+          <t>Cournonsec</t>
+        </is>
+      </c>
+      <c r="C144" s="14" t="inlineStr"/>
+      <c r="D144" s="14" t="inlineStr">
+        <is>
+          <t>Cournonsec</t>
+        </is>
+      </c>
+      <c r="E144" s="14" t="inlineStr"/>
+      <c r="F144" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G144" s="14" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H144" s="14" t="inlineStr"/>
+      <c r="I144" s="14" t="inlineStr">
+        <is>
+          <t>20/03/2025</t>
+        </is>
+      </c>
+      <c r="J144" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="K144" s="14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L144" s="14" t="inlineStr"/>
+      <c r="M144" s="14" t="inlineStr"/>
+      <c r="N144" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P144" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B144" s="17" t="inlineStr"/>
-      <c r="C144" s="17" t="inlineStr"/>
-      <c r="D144" s="17" t="inlineStr"/>
-      <c r="E144" s="17" t="inlineStr"/>
-      <c r="F144" s="17" t="inlineStr"/>
-      <c r="G144" s="17" t="inlineStr"/>
-      <c r="H144" s="17" t="inlineStr"/>
-      <c r="I144" s="17" t="inlineStr"/>
-      <c r="J144" s="17" t="inlineStr"/>
-      <c r="K144" s="17" t="inlineStr"/>
-      <c r="L144" s="17" t="inlineStr"/>
-      <c r="M144" s="17" t="inlineStr"/>
-      <c r="N144" s="18" t="n">
+      <c r="B145" s="17" t="inlineStr"/>
+      <c r="C145" s="17" t="inlineStr"/>
+      <c r="D145" s="17" t="inlineStr"/>
+      <c r="E145" s="17" t="inlineStr"/>
+      <c r="F145" s="17" t="inlineStr"/>
+      <c r="G145" s="17" t="inlineStr"/>
+      <c r="H145" s="17" t="inlineStr"/>
+      <c r="I145" s="17" t="inlineStr"/>
+      <c r="J145" s="17" t="inlineStr"/>
+      <c r="K145" s="17" t="inlineStr"/>
+      <c r="L145" s="17" t="inlineStr"/>
+      <c r="M145" s="17" t="inlineStr"/>
+      <c r="N145" s="18" t="n">
         <v>64017.394</v>
       </c>
-      <c r="O144" s="18" t="n">
-        <v>21098.53</v>
-      </c>
-      <c r="P144" s="18" t="n">
-        <v>101.92</v>
+      <c r="O145" s="18" t="n">
+        <v>21694.23</v>
+      </c>
+      <c r="P145" s="18" t="n">
+        <v>104.67</v>
       </c>
     </row>
   </sheetData>
@@ -10903,6 +10963,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId137"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId140"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11606,7 +11667,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>151.75</v>
+        <v>152</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>29.5</v>
@@ -11615,7 +11676,7 @@
         <v>10</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>191.25</v>
+        <v>191.5</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>66.25</v>
@@ -11752,10 +11813,10 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>376276</v>
+        <v>375680</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>143042</v>
+        <v>142446</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>233234</v>
@@ -11777,10 +11838,10 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>168133</v>
+        <v>167537</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>64211</v>
+        <v>63615</v>
       </c>
       <c r="D6" s="25" t="n">
         <v>103922</v>
@@ -11831,7 +11892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -11855,7 +11916,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 14 commande(s)</t>
+          <t>Épics créées ce mois — 13 commande(s)</t>
         </is>
       </c>
     </row>
@@ -11910,12 +11971,12 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35236</t>
+          <t>PDMDEP-35212</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35227</t>
+          <t>PDMDEP-35206</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
@@ -11925,7 +11986,7 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE CHAUNY</t>
+          <t>VILLE DE BOULOGNE-BILLANCOURT</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -11935,7 +11996,7 @@
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -11945,7 +12006,7 @@
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>00179114</t>
+          <t>00179038</t>
         </is>
       </c>
       <c r="I5" s="25" t="n">
@@ -11955,22 +12016,22 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35212</t>
+          <t>PDMDEP-35171</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35206</t>
+          <t>PDMDEP-35165</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BOULOGNE-BILLANCOURT</t>
+          <t>MAIRIE DE LORGUES</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -11990,22 +12051,22 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>00179038</t>
+          <t>00178865</t>
         </is>
       </c>
       <c r="I6" s="26" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35171</t>
+          <t>PDMDEP-35156</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35165</t>
+          <t>PDMDEP-35148</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
@@ -12015,7 +12076,7 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LORGUES</t>
+          <t>Mairie de Les Portes En Ré</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -12035,32 +12096,32 @@
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>00178865</t>
+          <t>00178841</t>
         </is>
       </c>
       <c r="I7" s="25" t="n">
-        <v>800</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35156</t>
+          <t>PDMDEP-35139</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35148</t>
+          <t>PDMDEP-35130</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Mairie de Les Portes En Ré</t>
+          <t>COMMUNE DE HARNES</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -12070,7 +12131,7 @@
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
@@ -12080,22 +12141,22 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>00178841</t>
+          <t>00178821</t>
         </is>
       </c>
       <c r="I8" s="26" t="n">
-        <v>250</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35139</t>
+          <t>PDMDEP-35114</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35130</t>
+          <t>PDMDEP-35105</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
@@ -12105,7 +12166,7 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE HARNES</t>
+          <t>MAIRIE DE CARNAC</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -12125,22 +12186,22 @@
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>00178821</t>
+          <t>00178806</t>
         </is>
       </c>
       <c r="I9" s="25" t="n">
-        <v>2035</v>
+        <v>985</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35114</t>
+          <t>PDMDEP-35088</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35105</t>
+          <t>PDMDEP-35082</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -12150,7 +12211,7 @@
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CARNAC</t>
+          <t>FREJUS</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -12170,32 +12231,32 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>00178806</t>
+          <t>00152501</t>
         </is>
       </c>
       <c r="I10" s="26" t="n">
-        <v>985</v>
+        <v>3541.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35088</t>
+          <t>PDMDEP-35008</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35082</t>
+          <t>PDMDEP-35000</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>FREJUS</t>
+          <t>COMMUNE DE PALAVAS-LES-FLOTS</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -12205,7 +12266,7 @@
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -12215,32 +12276,32 @@
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>00152501</t>
+          <t>00178436</t>
         </is>
       </c>
       <c r="I11" s="25" t="n">
-        <v>3541.5</v>
+        <v>500</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35008</t>
+          <t>PDMDEP-34961</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35000</t>
+          <t>PDMDEP-34953</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE PALAVAS-LES-FLOTS</t>
+          <t>COMMUNE DE BAIE-MAHAULT</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -12260,37 +12321,37 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>00178436</t>
+          <t>00178176</t>
         </is>
       </c>
       <c r="I12" s="26" t="n">
-        <v>500</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34961</t>
+          <t>PDMDEP-35188</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34953</t>
+          <t>PDMDEP-35184</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BAIE-MAHAULT</t>
+          <t>COMMUNE DE GAILLARD</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
@@ -12305,32 +12366,32 @@
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>00178176</t>
+          <t>00178947</t>
         </is>
       </c>
       <c r="I13" s="25" t="n">
-        <v>4050</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35188</t>
+          <t>PDMDEP-35041</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35184</t>
+          <t>PDMDEP-35037</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE GAILLARD</t>
+          <t xml:space="preserve">VILLE DE VILLEFRANCHE SUR SAONE </t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -12350,32 +12411,32 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>00178947</t>
+          <t>00178778</t>
         </is>
       </c>
       <c r="I14" s="26" t="n">
-        <v>1736</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35041</t>
+          <t>PDMDEP-34993</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35037</t>
+          <t>PDMDEP-34989</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLE DE VILLEFRANCHE SUR SAONE </t>
+          <t>Commune de Villeneuve D'Ascq</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
@@ -12395,32 +12456,32 @@
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>00178778</t>
+          <t>00178306</t>
         </is>
       </c>
       <c r="I15" s="25" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34993</t>
+          <t>PDMDEP-34979</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34989</t>
+          <t>PDMDEP-34975</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Commune de Villeneuve D'Ascq</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
@@ -12440,32 +12501,32 @@
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>00178306</t>
+          <t>00178226</t>
         </is>
       </c>
       <c r="I16" s="26" t="n">
-        <v>1500</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34979</t>
+          <t>PDMDEP-34929</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34975</t>
+          <t>PDMDEP-34925</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t>COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
@@ -12485,62 +12546,38 @@
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>00178226</t>
+          <t>00178034</t>
         </is>
       </c>
       <c r="I17" s="25" t="n">
-        <v>2200</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34929</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34925</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>04/08/2026</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE</t>
-        </is>
-      </c>
-      <c r="E18" s="11" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
-      <c r="H18" s="11" t="inlineStr">
-        <is>
-          <t>00178034</t>
-        </is>
-      </c>
-      <c r="I18" s="26" t="n">
-        <v>2300</v>
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="17" t="n"/>
+      <c r="F18" s="17" t="n"/>
+      <c r="G18" s="17" t="n"/>
+      <c r="H18" s="17" t="inlineStr">
+        <is>
+          <t>13 commande(s)</t>
+        </is>
+      </c>
+      <c r="I18" s="24" t="n">
+        <v>19898</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B19" s="17" t="n"/>
@@ -12551,17 +12588,17 @@
       <c r="G19" s="17" t="n"/>
       <c r="H19" s="17" t="inlineStr">
         <is>
-          <t>14 commande(s)</t>
+          <t>5 commande(s)</t>
         </is>
       </c>
       <c r="I19" s="24" t="n">
-        <v>19898</v>
+        <v>7736</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="17" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>dont GEODP</t>
         </is>
       </c>
       <c r="B20" s="17" t="n"/>
@@ -12572,31 +12609,10 @@
       <c r="G20" s="17" t="n"/>
       <c r="H20" s="17" t="inlineStr">
         <is>
-          <t>5 commande(s)</t>
+          <t>8 commande(s)</t>
         </is>
       </c>
       <c r="I20" s="24" t="n">
-        <v>7736</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="17" t="inlineStr">
-        <is>
-          <t>dont GEODP</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="n"/>
-      <c r="C21" s="17" t="n"/>
-      <c r="D21" s="17" t="n"/>
-      <c r="E21" s="17" t="n"/>
-      <c r="F21" s="17" t="n"/>
-      <c r="G21" s="17" t="n"/>
-      <c r="H21" s="17" t="inlineStr">
-        <is>
-          <t>9 commande(s)</t>
-        </is>
-      </c>
-      <c r="I21" s="24" t="n">
         <v>12162</v>
       </c>
     </row>

--- a/jira_export_2026-08-25.xlsx
+++ b/jira_export_2026-08-25.xlsx
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>268</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -1103,16 +1103,8 @@
       <c r="K5" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="L5" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-35041</t>
-        </is>
-      </c>
-      <c r="M5" s="11" t="inlineStr">
-        <is>
-          <t>00178778</t>
-        </is>
-      </c>
+      <c r="L5" s="11" t="inlineStr"/>
+      <c r="M5" s="11" t="inlineStr"/>
       <c r="N5" s="12" t="n">
         <v>0</v>
       </c>
@@ -2085,7 +2077,7 @@
         <v>1</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
@@ -10818,7 +10810,7 @@
         <v>21694.23</v>
       </c>
       <c r="P145" s="18" t="n">
-        <v>104.67</v>
+        <v>104.55</v>
       </c>
     </row>
   </sheetData>
@@ -11667,7 +11659,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>152</v>
+        <v>152.25</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>29.5</v>
@@ -11676,7 +11668,7 @@
         <v>10</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>191.5</v>
+        <v>191.75</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>66.25</v>
@@ -11686,7 +11678,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>31.9%</t>
         </is>
       </c>
     </row>
@@ -11971,22 +11963,22 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35212</t>
+          <t>PDMDEP-35285</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35206</t>
+          <t>PDMDEP-35275</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE BOULOGNE-BILLANCOURT</t>
+          <t>COMMUNE DE TRETS</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -12006,7 +11998,7 @@
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>00179038</t>
+          <t>00179201</t>
         </is>
       </c>
       <c r="I5" s="25" t="n">
@@ -12016,22 +12008,22 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35171</t>
+          <t>PDMDEP-35212</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35165</t>
+          <t>PDMDEP-35206</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LORGUES</t>
+          <t>VILLE DE BOULOGNE-BILLANCOURT</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -12051,22 +12043,22 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>00178865</t>
+          <t>00179038</t>
         </is>
       </c>
       <c r="I6" s="26" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35156</t>
+          <t>PDMDEP-35171</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35148</t>
+          <t>PDMDEP-35165</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
@@ -12076,7 +12068,7 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>Mairie de Les Portes En Ré</t>
+          <t>MAIRIE DE LORGUES</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -12096,32 +12088,32 @@
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>00178841</t>
+          <t>00178865</t>
         </is>
       </c>
       <c r="I7" s="25" t="n">
-        <v>250</v>
+        <v>800</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35139</t>
+          <t>PDMDEP-35156</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35130</t>
+          <t>PDMDEP-35148</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE HARNES</t>
+          <t>Mairie de Les Portes En Ré</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -12131,7 +12123,7 @@
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
@@ -12141,22 +12133,22 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>00178821</t>
+          <t>00178841</t>
         </is>
       </c>
       <c r="I8" s="26" t="n">
-        <v>2035</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35114</t>
+          <t>PDMDEP-35139</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35105</t>
+          <t>PDMDEP-35130</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
@@ -12166,7 +12158,7 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE CARNAC</t>
+          <t>COMMUNE DE HARNES</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -12186,22 +12178,22 @@
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>00178806</t>
+          <t>00178821</t>
         </is>
       </c>
       <c r="I9" s="25" t="n">
-        <v>985</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35088</t>
+          <t>PDMDEP-35114</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35082</t>
+          <t>PDMDEP-35105</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -12211,7 +12203,7 @@
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>FREJUS</t>
+          <t>MAIRIE DE CARNAC</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -12231,32 +12223,32 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>00152501</t>
+          <t>00178806</t>
         </is>
       </c>
       <c r="I10" s="26" t="n">
-        <v>3541.5</v>
+        <v>985</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35008</t>
+          <t>PDMDEP-35088</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35000</t>
+          <t>PDMDEP-35082</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE PALAVAS-LES-FLOTS</t>
+          <t>FREJUS</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -12266,7 +12258,7 @@
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -12276,32 +12268,32 @@
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>00178436</t>
+          <t>00152501</t>
         </is>
       </c>
       <c r="I11" s="25" t="n">
-        <v>500</v>
+        <v>3541.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34961</t>
+          <t>PDMDEP-35008</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34953</t>
+          <t>PDMDEP-35000</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BAIE-MAHAULT</t>
+          <t>COMMUNE DE PALAVAS-LES-FLOTS</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -12321,37 +12313,37 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>00178176</t>
+          <t>00178436</t>
         </is>
       </c>
       <c r="I12" s="26" t="n">
-        <v>4050</v>
+        <v>500</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35188</t>
+          <t>PDMDEP-34961</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35184</t>
+          <t>PDMDEP-34953</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE GAILLARD</t>
+          <t>COMMUNE DE BAIE-MAHAULT</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
@@ -12366,32 +12358,32 @@
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>00178947</t>
+          <t>00178176</t>
         </is>
       </c>
       <c r="I13" s="25" t="n">
-        <v>1736</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35041</t>
+          <t>PDMDEP-35188</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35037</t>
+          <t>PDMDEP-35184</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLE DE VILLEFRANCHE SUR SAONE </t>
+          <t>COMMUNE DE GAILLARD</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -12411,11 +12403,11 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>00178778</t>
+          <t>00178947</t>
         </is>
       </c>
       <c r="I14" s="26" t="n">
-        <v>0</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="15">
@@ -12588,7 +12580,7 @@
       <c r="G19" s="17" t="n"/>
       <c r="H19" s="17" t="inlineStr">
         <is>
-          <t>5 commande(s)</t>
+          <t>4 commande(s)</t>
         </is>
       </c>
       <c r="I19" s="24" t="n">
@@ -12609,7 +12601,7 @@
       <c r="G20" s="17" t="n"/>
       <c r="H20" s="17" t="inlineStr">
         <is>
-          <t>8 commande(s)</t>
+          <t>9 commande(s)</t>
         </is>
       </c>
       <c r="I20" s="24" t="n">

--- a/jira_export_2026-08-25.xlsx
+++ b/jira_export_2026-08-25.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>21,694 €</t>
+          <t>21,987 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -760,7 +760,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>9,545 €</t>
+          <t>9,838 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>388 h</t>
+          <t>400 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="14" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="L6" s="14" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -1509,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>1</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>1</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         <v>3</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>7.38</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
@@ -4669,10 +4669,10 @@
         <v>625</v>
       </c>
       <c r="O55" s="12" t="n">
-        <v>652.5</v>
+        <v>945</v>
       </c>
       <c r="P55" s="12" t="n">
-        <v>88.47</v>
+        <v>112.84</v>
       </c>
     </row>
     <row r="56">
@@ -4725,7 +4725,7 @@
         <v>3</v>
       </c>
       <c r="K56" s="14" t="n">
-        <v>7.38</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>192</v>
       </c>
       <c r="P56" s="15" t="n">
-        <v>26.03</v>
+        <v>22.93</v>
       </c>
     </row>
     <row r="57">
@@ -7797,7 +7797,7 @@
         <v>9</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>0.85</v>
+        <v>1.05</v>
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>9</v>
       </c>
       <c r="K100" s="14" t="n">
-        <v>0.85</v>
+        <v>1.05</v>
       </c>
       <c r="L100" s="14" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>9</v>
       </c>
       <c r="K101" s="11" t="n">
-        <v>0.85</v>
+        <v>1.05</v>
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         <v>9</v>
       </c>
       <c r="K102" s="14" t="n">
-        <v>0.85</v>
+        <v>1.05</v>
       </c>
       <c r="L102" s="14" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>9</v>
       </c>
       <c r="K103" s="11" t="n">
-        <v>0.85</v>
+        <v>1.05</v>
       </c>
       <c r="L103" s="11" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         <v>9</v>
       </c>
       <c r="K104" s="14" t="n">
-        <v>1.25</v>
+        <v>4.25</v>
       </c>
       <c r="L104" s="14" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
         <v>35</v>
       </c>
       <c r="K134" s="14" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L134" s="14" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -10439,7 +10439,7 @@
         <v>35</v>
       </c>
       <c r="K138" s="14" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="L138" s="14" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -10807,10 +10807,10 @@
         <v>64017.394</v>
       </c>
       <c r="O145" s="18" t="n">
-        <v>21694.23</v>
+        <v>21986.73</v>
       </c>
       <c r="P145" s="18" t="n">
-        <v>104.55</v>
+        <v>101.2</v>
       </c>
     </row>
   </sheetData>
@@ -11659,16 +11659,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>152.25</v>
+        <v>160.25</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>29.5</v>
+        <v>30.5</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>10</v>
+        <v>10.75</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>191.75</v>
+        <v>201.5</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>66.25</v>
@@ -11678,7 +11678,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>33.5%</t>
         </is>
       </c>
     </row>
@@ -11720,7 +11720,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>106.25</v>
+        <v>108.25</v>
       </c>
     </row>
   </sheetData>
@@ -11805,16 +11805,16 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>375680</v>
+        <v>375387</v>
       </c>
       <c r="C5" s="24" t="n">
         <v>142446</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>233234</v>
+        <v>232941</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>146689</v>
+        <v>146396</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>21179</v>
@@ -11830,16 +11830,16 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>167537</v>
+        <v>167245</v>
       </c>
       <c r="C6" s="25" t="n">
         <v>63615</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>103922</v>
+        <v>103630</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>86732</v>
+        <v>86439</v>
       </c>
       <c r="F6" s="25" t="n">
         <v>11307</v>
